--- a/IndiceAplicacionesLibro/analizadoropenrouterymas/RECOMENDACIÓN CHATGPT PROYECTO.xlsx
+++ b/IndiceAplicacionesLibro/analizadoropenrouterymas/RECOMENDACIÓN CHATGPT PROYECTO.xlsx
@@ -174,7 +174,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,6 +184,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -223,6 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -554,7 +561,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -574,7 +581,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -594,7 +601,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -614,7 +621,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -634,7 +641,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -654,7 +661,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -734,7 +741,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -754,7 +761,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -774,7 +781,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">

--- a/IndiceAplicacionesLibro/analizadoropenrouterymas/RECOMENDACIÓN CHATGPT PROYECTO.xlsx
+++ b/IndiceAplicacionesLibro/analizadoropenrouterymas/RECOMENDACIÓN CHATGPT PROYECTO.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="46">
   <si>
     <t>Estructura</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>ANALIZADOR CHATGPT</t>
+  </si>
+  <si>
+    <t>EDITOR CHATGPT</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
